--- a/docs/test-cases/SPM-33_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-33_Test_Cases.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>A partly reserved equipment line prevents confirmation until it is marked as not required</t>
+          <t>An equipment line that cannot be provided prevents confirmation until it is marked as not required</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1205,7 +1205,7 @@
 src/app/api/events/[id]/route.ts
 src/app/events/[id]/readiness/page.tsx
 prisma/schema.prisma
-prisma/migrations/20261009100000_add_arrangement_not_required/migration.sql
+prisma/migrations/20261010100000_add_arrangement_not_required/migration.sql
 scripts/seed-spm33.ts
 prisma/seed.ts</t>
         </is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1">
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Partly Reserved' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and one equipment requirement: 2 Audio Mixing Desks, of which Technical Support reserved 1 (status Partially fulfilled). Logged in as Daniel Tan. This case confirms the event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="139" customHeight="1">
+          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Waive Then Confirm' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and two equipment requirements: 2 Audio Mixing Desks, of which Technical Support reserved 1 (status Partially fulfilled), and a Portable Stage marked 'Cannot be provided'. Logged in as Daniel Tan. This case confirms the event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1641,11 +1641,11 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Partly Reserved' in the list
+2. Click 'SPM33 Waive Then Confirm' in the list
 3. Click 'Confirm event'
 4. Click 'Confirm event' in the dialog
 5. Click the 'Readiness' tab
-6. Click 'Mark as not required' in the 'Audio Mixing Desk' item
+6. Click 'Mark as not required' in the 'Portable Stage' item
 7. Click the 'Overview' tab
 8. Click 'Confirm event'
 9. Click 'Confirm event' in the dialog</t>
@@ -1660,13 +1660,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM33 Partly Reserved (Planning)
+          <t>Event: SPM33 Waive Then Confirm (Planning)
 Venue: Orchard Gallery, Approved
-Equipment: Audio Mixing Desk, 2 requested, 1 reserved, Partially fulfilled</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="166" customHeight="1">
+Equipment: Audio Mixing Desk, 2 requested, 1 reserved, Partially fulfilled; Portable Stage, Cannot be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="193" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1674,9 +1674,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 4: The event is NOT confirmed. The message 'This event cannot be confirmed yet: Audio Mixing Desk for this event is only partly reserved.' is shown and the status badge still reads 'Planning'.
-Step 5: 'Audio Mixing Desk' shows 'Partially fulfilled' and 'Outstanding'. The message '1 arrangement still blocks confirmation' is shown.
-Step 6: 'Audio Mixing Desk' shows 'Not required'. The message changes to 'Nothing is blocking confirmation'.
+          <t>Step 4: The event is NOT confirmed. The message 'This event cannot be confirmed yet: Portable Stage for this event is not reserved yet.' is shown, and does not mention the Audio Mixing Desk. The status badge still reads 'Planning'.
+Step 5: 'Audio Mixing Desk' shows 'Partially fulfilled' and 'Complete', with no 'Mark as not required' button: Technical Support have reserved what they can. 'Portable Stage' shows 'Cannot be provided' and 'Outstanding'. The message '1 arrangement still blocks confirmation' is shown.
+Step 6: 'Portable Stage' shows 'Not required'. The message changes to 'Nothing is blocking confirmation'.
 Step 9: The message 'The event is confirmed. The organiser can now see the arrangements.' is shown and the status badge changes to 'Confirmed'.</t>
         </is>
       </c>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Written before the code (TDD, 2026-10-08); the code was built to these cases and the automated tests on 2026-10-09. The cases have NOT yet been walked through the running app: that needs the migration 20261009100000_add_arrangement_not_required applied to the shared database and npm run fixtures:spm33 run. Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
+          <t>Written before the code (TDD, 2026-10-08); the code was built to these cases and the automated tests on 2026-10-09. The cases have NOT yet been walked through the running app: the migration 20261010100000_add_arrangement_not_required was applied to the shared database on 2026-10-10, and npm run fixtures:spm33 still has to be run first. Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
@@ -2475,18 +2475,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08 (Kristen): what Confirm enforces in this story (AC11). Confirm refuses on every arrangement the Readiness tab shows as outstanding: an unbooked or pending venue, unreserved equipment, a flagged booking or equipment reservation, and incomplete registration setup. Arrangements marked as not required do not block. The safety check does not block Confirm in this story; that gate stays with Resolve Safety Check Outcome (SPM-88).</t>
+          <t>DECIDED 2026-10-08 (Kristen): what Confirm enforces in this story (AC11). Confirm refuses on every arrangement the Readiness tab shows as outstanding: an unbooked or pending venue, equipment that is neither Reserved nor Partially fulfilled, a flagged booking or equipment reservation, and incomplete registration setup. Arrangements marked as not required do not block. The safety check does not block Confirm in this story; that gate stays with Resolve Safety Check Outcome (SPM-88).</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
     </row>
-    <row r="6" ht="98.5" customHeight="1">
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08 (Kristen): equipment Technical Support could only partly reserve (Partially fulfilled) is outstanding until the Coordinator marks the line as not required (#90, #106). This changes Confirm Event (SPM-34): SPM-34-TC05 expects such an event to confirm and now needs the same steps as SPM-33-TC10. It also changes the message in SPM-34-TC07, which now names the venue: 'Orchard Seminar Room for this event is still awaiting a decision from Venue Staff'.</t>
+          <t>DECIDED 2026-10-08, from the design not the story: the screen is the event's Readiness tab (S-18 in UI_DESIGN.md), at /events/&lt;reference&gt;/readiness, shown after the Equipment tab. Only coordinators have it. Any coordinator can view it; only the assigned one can mark arrangements. Every other role sees 'You don't have access to this event.' (the Equipment tab's wording).</t>
         </is>
       </c>
       <c r="C6" s="11" t="n"/>
@@ -2497,40 +2497,40 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, from the design not the story: the screen is the event's Readiness tab (S-18 in UI_DESIGN.md), at /events/&lt;reference&gt;/readiness, shown after the Equipment tab. Only coordinators have it. Any coordinator can view it; only the assigned one can mark arrangements. Every other role sees 'You don't have access to this event.' (the Equipment tab's wording).</t>
+          <t>DECIDED 2026-10-08, not in the story: arrangements can be marked as not required, or as required again, only while the event is in Planning. On a Confirmed event, reversing a decision would leave a confirmed event with something outstanding (SPM-33-TC12). The server's refusal reads 'Arrangements can only be marked as not required while the event is in Planning.'</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
     </row>
-    <row r="8" ht="85" customHeight="1">
+    <row r="8" ht="71.5" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, not in the story: arrangements can be marked as not required, or as required again, only while the event is in Planning. On a Confirmed event, reversing a decision would leave a confirmed event with something outstanding (SPM-33-TC12). The server's refusal reads 'Arrangements can only be marked as not required while the event is in Planning.'</t>
+          <t>DECIDED 2026-10-08, not in the story: only an outstanding arrangement offers 'Mark as not required'. A complete one (an approved booking, reserved equipment) has nothing to waive; to drop it the Coordinator withdraws the booking or removes the requirement. The server's refusal reads 'Only an outstanding arrangement can be marked as not required.'</t>
         </is>
       </c>
       <c r="C8" s="11" t="n"/>
     </row>
-    <row r="9" ht="71.5" customHeight="1">
+    <row r="9" ht="166" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, not in the story: only an outstanding arrangement offers 'Mark as not required'. A complete one (an approved booking, reserved equipment) has nothing to waive; to drop it the Coordinator withdraws the booking or removes the requirement. The server's refusal reads 'Only an outstanding arrangement can be marked as not required.'</t>
+          <t>DECIDED 2026-10-09 (Kristen): who marked an arrangement as not required, and when, is recorded and shown on the item: 'Marked as not required by Daniel Tan on 8 Oct 2026, 11:00' (SPM-33-TC05, SPM-33-TC12). The customer briefing asks for it: 'Significant actions are recorded, including who performed the action and when it occurred' (Activity History), 'ConnectSphere should be able to determine what was changed, who changed it, and when' (8f Auditability, and answer #14). Reversing is stamped the same way, so the record is the latest decision on each arrangement, not a full history; answer #96 says a complete audit-history function is not required for Release 1. Marking still takes one click with no confirmation dialog, and no reason is asked for: none of the documents require one. Say so if the team wants a reason kept.</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
     </row>
-    <row r="10" ht="166" customHeight="1">
+    <row r="10" ht="125.5" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09 (Kristen): who marked an arrangement as not required, and when, is recorded and shown on the item: 'Marked as not required by Daniel Tan on 8 Oct 2026, 11:00' (SPM-33-TC05, SPM-33-TC12). The customer briefing asks for it: 'Significant actions are recorded, including who performed the action and when it occurred' (Activity History), 'ConnectSphere should be able to determine what was changed, who changed it, and when' (8f Auditability, and answer #14). Reversing is stamped the same way, so the record is the latest decision on each arrangement, not a full history; answer #96 says a complete audit-history function is not required for Release 1. Marking still takes one click with no confirmation dialog, and no reason is asked for: none of the documents require one. Say so if the team wants a reason kept.</t>
+          <t>DECIDED 2026-10-08, wording: the state labels 'Complete', 'Outstanding' and 'Not required'; the buttons 'Mark as not required' and 'Mark as required'; the summary '2 arrangements still block confirmation', '1 arrangement still blocks confirmation' and 'Nothing is blocking confirmation'; the items 'No venue booked' and 'Registration setup'; and the reasons 'is still awaiting a decision from Venue Staff', 'is not reserved yet', 'is flagged for review: &lt;why&gt;', 'registration is enabled but has no capacity' and 'registration is enabled but has no registration period'.</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
@@ -2541,51 +2541,51 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, wording: the state labels 'Complete', 'Outstanding' and 'Not required'; the buttons 'Mark as not required' and 'Mark as required'; the summary '2 arrangements still block confirmation', '1 arrangement still blocks confirmation' and 'Nothing is blocking confirmation'; the items 'No venue booked' and 'Registration setup'; and the reasons 'is still awaiting a decision from Venue Staff', 'is not reserved yet', 'is only partly reserved', 'is flagged for review: &lt;why&gt;', 'registration is enabled but has no capacity' and 'registration is enabled but has no registration period'.</t>
+          <t>DECIDED 2026-10-08, not in the story: what is listed. One item per pending or approved venue booking (a rejected or cancelled request is not listed), one item per equipment line, and 'Registration setup' only while registration is enabled. An event with registration switched off has no registration item (SPM-33-TC02), although the mockup design/mockups/Readiness.dc.html shows one reading 'Not required'. The mockup's 'Request reviewed and approved' and 'Technical support assigned' items are not listed either: nothing assigns technical support staff to an event yet.</t>
         </is>
       </c>
       <c r="C11" s="11" t="n"/>
     </row>
-    <row r="12" ht="125.5" customHeight="1">
+    <row r="12" ht="58" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, not in the story: what is listed. One item per pending or approved venue booking (a rejected or cancelled request is not listed), one item per equipment line, and 'Registration setup' only while registration is enabled. An event with registration switched off has no registration item (SPM-33-TC02), although the mockup design/mockups/Readiness.dc.html shows one reading 'Not required'. The mockup's 'Request reviewed and approved' and 'Technical support assigned' items are not listed either: nothing assigns technical support staff to an event yet.</t>
+          <t>DECIDED 2026-10-08, not in the story: the Readiness tab has no 'Confirm event' button, although the mockup shows one. Confirming stays on the Overview (SPM-34), which is why SPM-33-TC01 and SPM-33-TC10 go back to it.</t>
         </is>
       </c>
       <c r="C12" s="11" t="n"/>
     </row>
-    <row r="13" ht="58" customHeight="1">
+    <row r="13" ht="125.5" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, not in the story: the Readiness tab has no 'Confirm event' button, although the mockup shows one. Confirming stays on the Overview (SPM-34), which is why SPM-33-TC01 and SPM-33-TC10 go back to it.</t>
+          <t>For Kayal (SPM-81) and Janelle (equipment, SPM-86): the migration 20261010100000_add_arrangement_not_required adds not_required, not_required_by and not_required_at to venue_bookings and to equipment_requests, which are their tables. It was applied to the shared database on 2026-10-10 and only adds columns. When SPM-81 is merged in, SPM-33-TC01 and SPM-33-TC07 should be run again with bookings made through its screen. When SPM-86 is merged in, add the safety check item (AC6, AC9) as the header of src/lib/eventConfirmation.ts describes, and its cases here.</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
     </row>
-    <row r="14" ht="112" customHeight="1">
+    <row r="14" ht="85" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>For Kayal (SPM-81) and Janelle (equipment, SPM-86): the migration 20261009100000_add_arrangement_not_required adds not_required, not_required_by and not_required_at to venue_bookings and to equipment_requests, which are their tables. Agree it in the team chat before it is applied. When SPM-81 is merged in, SPM-33-TC01 and SPM-33-TC07 should be run again with bookings made through its screen. When SPM-86 is merged in, add the safety check item (AC6, AC9) as the header of src/lib/eventConfirmation.ts describes, and its cases here.</t>
+          <t>To check when Review Flagged Arrangements (SPM-68) is built: AC4 says a flagged arrangement is outstanding 'until the Coordinator resolves it'. Resolving is SPM-68's; in this story the only way a flagged arrangement stops blocking is to be marked as not required. Is that an acceptable way to resolve a flagged booking, or should a flagged arrangement not offer 'Mark as not required'?</t>
         </is>
       </c>
       <c r="C14" s="11" t="n"/>
     </row>
-    <row r="15" ht="85" customHeight="1">
+    <row r="15" ht="71.5" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>To check when Review Flagged Arrangements (SPM-68) is built: AC4 says a flagged arrangement is outstanding 'until the Coordinator resolves it'. Resolving is SPM-68's; in this story the only way a flagged arrangement stops blocking is to be marked as not required. Is that an acceptable way to resolve a flagged booking, or should a flagged arrangement not offer 'Mark as not required'?</t>
+          <t>Merged with main on 2026-10-10, which brought Submit Event for Operational Safety Check (SPM-86). An arrangement marked as not required here no longer stops 'Submit for safety check' either (SPM-86 AC1: 'reserved or marked as not required'). AC6 and AC9 above can now be built: the Safety review status and the SafetyCheck record exist.</t>
         </is>
       </c>
       <c r="C15" s="11" t="n"/>

--- a/docs/test-cases/SPM-33_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-33_Test_Cases.xlsx
@@ -22,6 +22,9 @@
     <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="TC13" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="TC14" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="TC15" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TC16" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="TC17" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -461,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -533,12 +536,12 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Every venue booking and equipment line is listed with its own status, and Confirm names the outstanding ones</t>
+          <t>Every venue booking, equipment line and the safety check are listed with their own status, and Confirm names what is outstanding</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>AC1, AC2, AC3, AC7, AC11</t>
+          <t>AC1, AC2, AC3, AC6, AC7, AC9, AC11</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -629,12 +632,12 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>A flagged venue booking and equipment reservation are shown as outstanding, with why, and prevent confirmation</t>
+          <t>A second venue requested from the Venue tab is listed on its own, beside the first</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>AC4, AC11</t>
+          <t>AC2, AC1</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -661,12 +664,12 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>The assigned Coordinator marks an equipment line Technical Support cannot provide as not required</t>
+          <t>A flagged venue booking and equipment reservation are shown as outstanding, with why, and prevent confirmation</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>AC8, AC10, AC7</t>
+          <t>AC4, AC11</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -693,12 +696,12 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>The Coordinator reverses a not-required decision and the arrangement is outstanding again</t>
+          <t>An event with the Safety Officer shows its safety check as awaiting review, and nothing can be marked</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>AC8</t>
+          <t>AC6, AC11</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -725,12 +728,12 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>One of two venue bookings is marked as not required and the other is unchanged</t>
+          <t>A decided safety check shows the Safety Officer's decision</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>AC8, AC2</t>
+          <t>AC6, AC7</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -757,17 +760,17 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Marking an event's only venue booking as not required still leaves it without a venue</t>
+          <t>The assigned Coordinator marks an equipment line Technical Support cannot provide as not required</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>AC8, AC11</t>
+          <t>AC8, AC10, AC7</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -789,12 +792,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Registration that is enabled but has no capacity is outstanding until it is marked as not required</t>
+          <t>The Coordinator reverses a not-required decision and the arrangement is outstanding again</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>AC5, AC8</t>
+          <t>AC8</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -821,12 +824,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>An equipment line that cannot be provided prevents confirmation until it is marked as not required</t>
+          <t>One of two venue bookings is marked as not required and the other is unchanged</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>AC11, AC8</t>
+          <t>AC8, AC2</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -853,17 +856,17 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>A Coordinator who is not the assigned one can view the arrangements but cannot mark them</t>
+          <t>Marking an event's only venue booking as not required still leaves it without a venue</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>AC8</t>
+          <t>AC8, AC11</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -885,17 +888,17 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>On a Confirmed event a not-required arrangement is shown as such and can no longer be changed</t>
+          <t>Registration that is enabled but has no capacity is outstanding until it is marked as not required</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>AC8, AC10</t>
+          <t>AC5, AC8</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -917,17 +920,17 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>An Event Organiser has no Readiness tab and cannot open it by its address</t>
+          <t>An equipment line that cannot be provided prevents confirmation until it is marked as not required</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>AC1</t>
+          <t>AC11, AC8</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -949,296 +952,444 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
+          <t>A Coordinator who is not the assigned one can view the arrangements but cannot mark them</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>AC8</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>TC15</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC15</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>On a Confirmed event a not-required arrangement is shown as such and can no longer be changed</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>AC8, AC10</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>TC16</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC16</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>An Event Organiser has no Readiness tab and cannot open it by its address</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>AC1</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>TC17</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC17</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
           <t>A visitor who is not logged in is sent to log in</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
       </c>
-      <c r="F20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="71.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="F23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>The system displays outstanding venue arrangements.</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>SPM-33-TC01
 SPM-33-TC02
 SPM-33-TC03
-SPM-33-TC13
-SPM-33-TC14</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="44.5" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+SPM-33-TC04
+SPM-33-TC16
+SPM-33-TC17</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Given an event has more than one venue booking, when arrangements are displayed, then each venue booking is listed separately with its own status (see: Request More Than One Venue for an Event, SPM-81).</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>SPM-33-TC01
-SPM-33-TC03
-SPM-33-TC07</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="17.5" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>AC3</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>The system displays outstanding equipment arrangements.</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>SPM-33-TC01</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>AC4</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Given a venue booking or equipment reservation is flagged for review, when arrangements are displayed, then it is shown as outstanding, with why it was flagged, until the Coordinator resolves it (see: Review Flagged Arrangements, SPM-68).</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>SPM-33-TC04</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="44.5" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>AC5</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>The system displays other required planning items, including registration setup that is enabled but incomplete (see: Configure Event Registration, SPM-64).</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>SPM-33-TC02
-SPM-33-TC09</t>
+          <t>SPM-33-TC01
+SPM-33-TC03
+SPM-33-TC04
+SPM-33-TC10</t>
         </is>
       </c>
       <c r="F25" s="9" t="n"/>
     </row>
-    <row r="26" ht="31" customHeight="1">
+    <row r="26" ht="17.5" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>AC7</t>
+          <t>AC3</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Completed arrangements are distinguishable from outstanding ones.</t>
+          <t>The system displays outstanding equipment arrangements.</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>SPM-33-TC01
-SPM-33-TC05</t>
+          <t>SPM-33-TC01</t>
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
     </row>
-    <row r="27" ht="112" customHeight="1">
+    <row r="27" ht="58" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>AC8</t>
+          <t>AC4</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>The assigned Coordinator can mark an arrangement as not required for this event (e.g. an event that needs no equipment, or an unfulfilled equipment item agreed with Technical Support Staff to be non-essential), and can reverse that decision.</t>
+          <t>Given a venue booking or equipment reservation is flagged for review, when arrangements are displayed, then it is shown as outstanding, with why it was flagged, until the Coordinator resolves it (see: Review Flagged Arrangements, SPM-68).</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>SPM-33-TC05
+          <t>SPM-33-TC05</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="44.5" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>AC5</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>The system displays other required planning items, including registration setup that is enabled but incomplete (see: Configure Event Registration, SPM-64).</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC02
+SPM-33-TC12</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>The Operational Safety Check is displayed as a required item, showing whether it is not yet submitted, awaiting review, approved, or returned with changes or a rejection (see: Submit Event for Operational Safety Check, SPM-86).</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC01
 SPM-33-TC06
+SPM-33-TC07</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="44.5" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>AC7</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Completed arrangements are distinguishable from outstanding ones.</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC01
 SPM-33-TC07
-SPM-33-TC08
+SPM-33-TC08</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="112" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>AC8</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>The assigned Coordinator can mark an arrangement as not required for this event (e.g. an event that needs no equipment, or an unfulfilled equipment item agreed with Technical Support Staff to be non-essential), and can reverse that decision.</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC08
 SPM-33-TC09
 SPM-33-TC10
 SPM-33-TC11
-SPM-33-TC12</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="31" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+SPM-33-TC12
+SPM-33-TC13
+SPM-33-TC14
+SPM-33-TC15</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>AC9</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>The Operational Safety Check cannot be marked as not required.</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC01</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="31" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>AC10</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>An arrangement marked as not required is shown as such and is distinguishable from both completed and outstanding arrangements.</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>SPM-33-TC05
-SPM-33-TC12</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>SPM-33-TC08
+SPM-33-TC15</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="71.5" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>AC11</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>The Coordinator can identify which arrangements are preventing confirmation; arrangements marked as not required do not prevent it.</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>SPM-33-TC01
-SPM-33-TC04
-SPM-33-TC08
-SPM-33-TC10</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="n"/>
-    </row>
-    <row r="31" ht="179.5" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+SPM-33-TC05
+SPM-33-TC06
+SPM-33-TC11
+SPM-33-TC13</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n"/>
+    </row>
+    <row r="36" ht="206.5" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>src/lib/eventConfirmation.ts
-src/lib/eventArrangements.ts
-src/lib/permissions.ts
-src/lib/statuses.ts
-src/lib/eventTabs.ts
-src/lib/validation/events.ts
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>prisma/migrations/20261010100000_add_arrangement_not_required/migration.sql
+prisma/schema.prisma
+prisma/seed.ts
+scripts/seed-spm33.ts
 src/app/api/events/[id]/arrangements/route.ts
 src/app/api/events/[id]/route.ts
+src/app/api/events/[id]/safety-check/route.ts
 src/app/events/[id]/readiness/page.tsx
-prisma/schema.prisma
-prisma/migrations/20261010100000_add_arrangement_not_required/migration.sql
-scripts/seed-spm33.ts
-prisma/seed.ts</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="9" t="n"/>
+src/lib/eventArrangements.ts
+src/lib/eventConfirmation.ts
+src/lib/eventTabs.ts
+src/lib/permissions.ts
+src/lib/safetyCheck.ts
+src/lib/statuses.ts
+src/lib/validation/events.ts</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B31:F31"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="E31:F31"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E32:F32"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1255,6 +1406,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1266,7 +1420,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -1293,102 +1447,107 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>The assigned Coordinator marks an equipment line Technical Support cannot provide as not required</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Single Pending Room' is in Planning, assigned to Daniel Tan, with one venue booking, Orchard Studio (Pending), and no equipment. Logged in as Daniel Tan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Run npm run fixtures:spm33 before this case. 'SPM33 Stage Unavailable' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and two equipment requirements: Handheld Wireless Mic (Reserved) and Portable Stage, which Technical Support marked 'Cannot be provided'. Logged in as Daniel Tan. This case changes the event. SPM-33-TC09 needs that change, so go straight to it and run npm run fixtures:spm33 after SPM-33-TC09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Single Pending Room' in the list
+2. Click 'SPM33 Stage Unavailable' in the list
 3. Click the 'Readiness' tab
-4. Click 'Mark as not required' in the 'Orchard Studio' item</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+4. Click 'Mark as not required' in the 'Portable Stage' item</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Single Pending Room (Planning)
-Venue bookings: Orchard Studio (Pending) only</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="112" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Stage Unavailable (Planning)
+Venue: Orchard Gallery, Approved
+Equipment: Handheld Wireless Mic (Reserved), Portable Stage (Cannot be provided)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="166" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: 'Orchard Studio' shows 'Pending' and 'Outstanding'. There is no 'No venue booked' item. The message '1 arrangement still blocks confirmation' is shown.
-Step 4: 'Orchard Studio' shows 'Not required'. A new item 'No venue booked' appears showing 'Outstanding', with no 'Mark as not required' button. The message still reads '1 arrangement still blocks confirmation': an event always needs a venue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: 'Portable Stage' shows 'Cannot be provided' and 'Outstanding', with a 'Mark as not required' button. 'Orchard Gallery' and 'Handheld Wireless Mic' show 'Complete' and have no such button. The message '1 arrangement still blocks confirmation' is shown.
+Step 4: 'Portable Stage' now shows 'Not required' in place of 'Outstanding', and still shows 'Cannot be provided'. It says 'Marked as not required by Daniel Tan on' followed by today's date and the time. It reads differently from 'Handheld Wireless Mic', which shows 'Complete'. Its button now reads 'Mark as required'. The message changes to 'Nothing is blocking confirmation'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -1396,7 +1555,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1404,7 +1563,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -1412,10 +1571,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1428,7 +1595,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -1455,105 +1622,104 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>The Coordinator reverses a not-required decision and the arrangement is outstanding again</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Registration Not Needed' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and no equipment. Registration is enabled with an opening and closing date but no capacity. Logged in as Daniel Tan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>SPM-33-TC08 has just been run (so 'Portable Stage' on 'SPM33 Stage Unavailable' shows 'Not required') and the fixtures have NOT been reset since. Still logged in as Daniel Tan, on the Readiness tab of 'SPM33 Stage Unavailable'. Run npm run fixtures:spm33 after this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Registration Not Needed' in the list
-3. Click the 'Readiness' tab
-4. Click 'Mark as not required' in the 'Registration setup' item
-5. Click the 'Overview' tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>1. Click 'Mark as required' in the 'Portable Stage' item
+2. Click the 'Equipment' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Registration Not Needed (Planning)
-Venue: Orchard Gallery, Approved
-Registration: enabled, capacity not set</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="166" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Stage Unavailable (Planning)
+Equipment: Portable Stage (Cannot be provided), marked as not required in SPM-33-TC08</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: 'Orchard Gallery' shows 'Complete'. A separate item 'Registration setup' shows 'Outstanding', says registration is enabled but has no capacity, and has a 'Mark as not required' button. The message '1 arrangement still blocks confirmation' is shown.
-Step 4: 'Registration setup' shows 'Not required' and its button reads 'Mark as required'. The message changes to 'Nothing is blocking confirmation'.
-Step 5: The status badge still reads 'Planning', and the Registration card still shows Capacity as '—' with the same opening and closing dates. The registration settings were not changed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 1: 'Portable Stage' shows 'Outstanding' again, with a 'Mark as not required' button, and no longer says who marked it as not required. The message changes back to '1 arrangement still blocks confirmation'.
+Step 2: The 'Portable Stage' requirement is still listed with the status 'Cannot be provided' and its requested quantity. Marking it and reversing the decision did not change or remove the requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -1561,7 +1727,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1569,7 +1735,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -1577,10 +1743,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1593,7 +1767,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -1620,110 +1794,108 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="98.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>One of two venue bookings is marked as not required and the other is unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Waive Then Confirm' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and two equipment requirements: 2 Audio Mixing Desks, of which Technical Support reserved 1 (status Partially fulfilled), and a Portable Stage marked 'Cannot be provided'. Logged in as Daniel Tan. This case confirms the event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="125.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Breakout Not Needed' is in Planning, assigned to Daniel Tan, with two venue bookings: Marina Auditorium (Approved) and Orchard Studio (Pending). It has no equipment. Logged in as Daniel Tan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="71.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Waive Then Confirm' in the list
-3. Click 'Confirm event'
-4. Click 'Confirm event' in the dialog
-5. Click the 'Readiness' tab
-6. Click 'Mark as not required' in the 'Portable Stage' item
-7. Click the 'Overview' tab
-8. Click 'Confirm event'
-9. Click 'Confirm event' in the dialog</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+2. Click 'SPM33 Breakout Not Needed' in the list
+3. Click the 'Readiness' tab
+4. Click 'Mark as not required' in the 'Orchard Studio' item
+5. Click the 'Venue' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Waive Then Confirm (Planning)
-Venue: Orchard Gallery, Approved
-Equipment: Audio Mixing Desk, 2 requested, 1 reserved, Partially fulfilled; Portable Stage, Cannot be provided</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="193" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Breakout Not Needed (Planning)
+Venue bookings: Marina Auditorium (Approved), Orchard Studio (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="139" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 4: The event is NOT confirmed. The message 'This event cannot be confirmed yet: Portable Stage for this event is not reserved yet.' is shown, and does not mention the Audio Mixing Desk. The status badge still reads 'Planning'.
-Step 5: 'Audio Mixing Desk' shows 'Partially fulfilled' and 'Complete', with no 'Mark as not required' button: Technical Support have reserved what they can. 'Portable Stage' shows 'Cannot be provided' and 'Outstanding'. The message '1 arrangement still blocks confirmation' is shown.
-Step 6: 'Portable Stage' shows 'Not required'. The message changes to 'Nothing is blocking confirmation'.
-Step 9: The message 'The event is confirmed. The organiser can now see the arrangements.' is shown and the status badge changes to 'Confirmed'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: 'Orchard Studio' shows 'Pending' and 'Outstanding'. The message '1 arrangement still blocks confirmation' is shown.
+Step 4: 'Orchard Studio' shows 'Not required' and still shows 'Pending'. 'Marina Auditorium' still shows 'Approved' and 'Complete'. The message changes to 'Nothing is blocking confirmation'.
+Step 5: Under 'Booking requests', the Orchard Studio request is still listed as 'Pending' and the Marina Auditorium booking as 'Approved'. Neither was withdrawn or changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -1731,7 +1903,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1739,7 +1911,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -1747,10 +1919,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1763,7 +1943,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -1790,102 +1970,106 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Marking an event's only venue booking as not required still leaves it without a venue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Another Coordinator' is in Planning and assigned to Priya Raj, not Daniel Tan. It has a venue booking at Orchard Studio (Pending) and a Portable Stage requirement marked 'Cannot be provided'. Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Single Pending Room' is in Planning, assigned to Daniel Tan, with one venue booking, Orchard Studio (Pending), and no equipment. Logged in as Daniel Tan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Another Coordinator' in the list
-3. Click the 'Readiness' tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="85" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+2. Click 'SPM33 Single Pending Room' in the list
+3. Click the 'Readiness' tab
+4. Click 'Mark as not required' in the 'Orchard Studio' item</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Another Coordinator (Planning), coordinator Priya Raj
-Venue: Orchard Studio (Pending)
-Equipment: Portable Stage (Cannot be provided)
-Account: daniel.tan@connectsphere.com (a Coordinator, but not the assigned one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Single Pending Room (Planning)
+Venue bookings: Orchard Studio (Pending) only</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: 'Orchard Studio' and 'Portable Stage' are listed, both showing 'Outstanding', and the message '2 arrangements still block confirmation' is shown. Neither item has a 'Mark as not required' button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: 'Orchard Studio' shows 'Pending' and 'Outstanding'. There is no 'No venue booked' item. The message '1 arrangement still blocks confirmation' is shown.
+Step 4: 'Orchard Studio' shows 'Not required'. A new item 'No venue booked' appears showing 'Outstanding', with no 'Mark as not required' button. The message still reads '1 arrangement still blocks confirmation': an event always needs a venue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -1893,7 +2077,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1901,7 +2085,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -1909,10 +2093,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1925,7 +2117,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -1952,102 +2144,109 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="98.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Registration that is enabled but has no capacity is outstanding until it is marked as not required</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Confirmed With Waiver' is Confirmed, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and a Portable Stage requirement that is 'Cannot be provided' and was marked as not required by Daniel Tan on 1 Oct 2026 at 10:00, before the event was confirmed. Logged in as Daniel Tan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Registration Not Needed' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and no equipment. Registration is enabled with an opening and closing date but no capacity. Logged in as Daniel Tan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="85" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Confirmed With Waiver' in the list
-3. Click the 'Readiness' tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+2. Click 'SPM33 Registration Not Needed' in the list
+3. Click the 'Readiness' tab
+4. Click 'Mark as not required' in the 'Registration setup' item
+5. Click the 'Overview' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Confirmed With Waiver (Confirmed)
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Registration Not Needed (Planning)
 Venue: Orchard Gallery, Approved
-Equipment: Portable Stage (Cannot be provided), marked as not required by Daniel Tan on 1 Oct 2026, 10:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+Registration: enabled, capacity not set</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="166" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: The event opens with the status badge 'Confirmed'.
-Step 3: 'Orchard Gallery' shows 'Complete'. 'Portable Stage' shows 'Not required' and 'Cannot be provided', and says 'Marked as not required by Daniel Tan on 1 Oct 2026, 10:00'. There is no 'Mark as required' or 'Mark as not required' button on any item: arrangements are marked only while the event is in Planning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: 'Orchard Gallery' shows 'Complete'. A separate item 'Registration setup' shows 'Outstanding', says registration is enabled but has no capacity, and has a 'Mark as not required' button. The message '1 arrangement still blocks confirmation' is shown.
+Step 4: 'Registration setup' shows 'Not required' and its button reads 'Mark as required'. The message changes to 'Nothing is blocking confirmation'.
+Step 5: The status badge still reads 'Planning', and the Registration card still shows Capacity as '—' with the same opening and closing dates. The registration settings were not changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -2055,7 +2254,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -2063,7 +2262,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -2071,10 +2270,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2087,7 +2294,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -2114,102 +2321,114 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). Rachel Ng (rachel.ng@meridianfina.com / password123) is the Event Organiser who raised 'SPM33 Two Room Conference'. Logged out.</t>
+          <t>An equipment line that cannot be provided prevents confirmation until it is marked as not required</t>
         </is>
       </c>
     </row>
     <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Waive Then Confirm' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and two equipment requirements: 2 Audio Mixing Desks, of which Technical Support reserved 1 (status Partially fulfilled), and a Portable Stage marked 'Cannot be provided'. Logged in as Daniel Tan. This case confirms the event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="125.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Log in as rachel.ng@meridianfina.com with password123
-2. Click 'My Events' in the sidebar
-3. Click 'SPM33 Two Room Conference' in the list
-4. Type /events/&lt;reference from step 3&gt;/readiness after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 3&gt;/readiness) and press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar
+2. Click 'SPM33 Waive Then Confirm' in the list
+3. Click 'Confirm event'
+4. Click 'Confirm event' in the dialog
+5. Click the 'Readiness' tab
+6. Click 'Mark as not required' in the 'Portable Stage' item
+7. Click the 'Overview' tab
+8. Click 'Confirm event'
+9. Click 'Confirm event' in the dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Account: rachel.ng@meridianfina.com (Event Organiser)
-Event: SPM33 Two Room Conference</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Waive Then Confirm (Planning)
+Venue: Orchard Gallery, Approved
+Equipment: Audio Mixing Desk, 2 requested, 1 reserved, Partially fulfilled; Portable Stage, Cannot be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="193" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: The event opens with its reference (EVT- followed by six digits) shown beside the title. The tabs do not include 'Readiness'.
-Step 4: The message 'You don't have access to this event.' is shown. No venue booking or equipment arrangement is listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 4: The event is NOT confirmed. The message 'This event cannot be confirmed yet: Portable Stage for this event is not reserved yet.' is shown, and does not mention the Audio Mixing Desk. The status badge still reads 'Planning'.
+Step 5: 'Audio Mixing Desk' shows 'Partially fulfilled' and 'Complete', with no 'Mark as not required' button: Technical Support have reserved what they can. 'Portable Stage' shows 'Cannot be provided' and 'Outstanding'. The message '1 arrangement still blocks confirmation' is shown.
+Step 6: 'Portable Stage' shows 'Not required'. The message changes to 'Nothing is blocking confirmation'.
+Step 9: The message 'The event is confirmed. The organiser can now see the arrangements.' is shown and the status badge changes to 'Confirmed'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -2217,7 +2436,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -2225,7 +2444,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -2233,10 +2452,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2249,7 +2476,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -2276,25 +2503,559 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>A Coordinator who is not the assigned one can view the arrangements but cannot mark them</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Another Coordinator' is in Planning and assigned to Priya Raj, not Daniel Tan. It has a venue booking at Orchard Studio (Pending) and a Portable Stage requirement marked 'Cannot be provided'. Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar
+2. Click 'SPM33 Another Coordinator' in the list
+3. Click the 'Readiness' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Another Coordinator (Planning), coordinator Priya Raj
+Venue: Orchard Studio (Pending)
+Equipment: Portable Stage (Cannot be provided)
+Account: daniel.tan@connectsphere.com (a Coordinator, but not the assigned one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: 'Orchard Studio' and 'Portable Stage' are listed, both showing 'Outstanding', and the message '2 arrangements still block confirmation' is shown. Neither item has a 'Mark as not required' button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-33-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+          <t>On a Confirmed event a not-required arrangement is shown as such and can no longer be changed</t>
         </is>
       </c>
     </row>
     <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Confirmed With Waiver' is Confirmed, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and a Portable Stage requirement that is 'Cannot be provided' and was marked as not required by Daniel Tan on 1 Oct 2026 at 10:00, before the event was confirmed. Logged in as Daniel Tan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar
+2. Click 'SPM33 Confirmed With Waiver' in the list
+3. Click the 'Readiness' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Confirmed With Waiver (Confirmed)
+Venue: Orchard Gallery, Approved
+Equipment: Portable Stage (Cannot be provided), marked as not required by Daniel Tan on 1 Oct 2026, 10:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="98.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 2: The event opens with the status badge 'Confirmed'.
+Step 3: 'Orchard Gallery' shows 'Complete'. 'Portable Stage' shows 'Not required' and 'Cannot be provided', and says 'Marked as not required by Daniel Tan on 1 Oct 2026, 10:00'. There is no 'Mark as required' or 'Mark as not required' button on any item: arrangements are marked only while the event is in Planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-33-TC16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>An Event Organiser has no Readiness tab and cannot open it by its address</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
       <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). Rachel Ng (rachel.ng@meridianfina.com / password123) is the Event Organiser who raised 'SPM33 Two Room Conference'. Logged out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="98.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>1. Log in as rachel.ng@meridianfina.com with password123
+2. Click 'My Events' in the sidebar
+3. Click 'SPM33 Two Room Conference' in the list
+4. Type /events/&lt;reference from step 3&gt;/readiness after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 3&gt;/readiness) and press Enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Account: rachel.ng@meridianfina.com (Event Organiser)
+Event: SPM33 Two Room Conference</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="85" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: The event opens with its reference (EVT- followed by six digits) shown beside the title. The tabs do not include 'Readiness'.
+Step 4: The message 'You don't have access to this event.' is shown. No venue booking or equipment arrangement is listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-33-TC17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17.5" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>A visitor who is not logged in is sent to log in</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="98.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM33 Two Room Conference' in the list
@@ -2303,75 +3064,67 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="31" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="6" ht="31" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Event: SPM33 Two Room Conference
 No account logged in at step 4</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Step 2: The event opens with its reference (EVT- followed by six digits) shown beside the title.
 Step 4: The Log in page is shown. No arrangements are visible.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -2379,7 +3132,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -2387,7 +3140,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -2395,10 +3148,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2411,7 +3172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2447,35 +3208,35 @@
       </c>
       <c r="C2" s="11" t="n"/>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>BLOCKED 2026-10-08, waiting for Submit Event for Operational Safety Check (SPM-86): AC6 ('The Operational Safety Check is displayed as a required item, showing whether it is not yet submitted, awaiting review, approved, or returned with changes or a rejection') and AC9 ('The Operational Safety Check cannot be marked as not required') have no test cases and no automated tests. SPM-86 defines the status they read, and nothing for it is merged. They keep their numbers, which is why the list above goes AC5, AC7, AC8, AC10. Add their cases when SPM-86 lands.</t>
+          <t>DECIDED 2026-10-08 (Kristen): what can be marked as not required (AC8). Any single venue booking, any equipment line and the registration setup. An event (or a session) with no pending or approved booking that is still required shows 'No venue booked', and that can never be marked as not required (SPM-33-TC02, SPM-33-TC11).</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
     </row>
-    <row r="4" ht="71.5" customHeight="1">
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08 (Kristen): what can be marked as not required (AC8). Any single venue booking, any equipment line and the registration setup. An event (or a session) with no pending or approved booking that is still required shows 'No venue booked', and that can never be marked as not required (SPM-33-TC02, SPM-33-TC08).</t>
+          <t>DECIDED 2026-10-08 (Kristen): what Confirm enforces in this story (AC11). Confirm refuses on every arrangement the Readiness tab shows as outstanding: an unbooked or pending venue, equipment that is neither Reserved nor Partially fulfilled, a flagged booking or equipment reservation, and incomplete registration setup. Arrangements marked as not required do not block. The safety check does not block Confirm in this story; that gate stays with Resolve Safety Check Outcome (SPM-88).</t>
         </is>
       </c>
       <c r="C4" s="11" t="n"/>
     </row>
-    <row r="5" ht="98.5" customHeight="1">
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08 (Kristen): what Confirm enforces in this story (AC11). Confirm refuses on every arrangement the Readiness tab shows as outstanding: an unbooked or pending venue, equipment that is neither Reserved nor Partially fulfilled, a flagged booking or equipment reservation, and incomplete registration setup. Arrangements marked as not required do not block. The safety check does not block Confirm in this story; that gate stays with Resolve Safety Check Outcome (SPM-88).</t>
+          <t>DECIDED 2026-10-08, from the design not the story: the screen is the event's Readiness tab (S-18 in UI_DESIGN.md), at /events/&lt;reference&gt;/readiness, shown after the Equipment tab. Only coordinators have it. Any coordinator can view it; only the assigned one can mark arrangements. Every other role sees 'You don't have access to this event.' (the Equipment tab's wording).</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -2486,40 +3247,40 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, from the design not the story: the screen is the event's Readiness tab (S-18 in UI_DESIGN.md), at /events/&lt;reference&gt;/readiness, shown after the Equipment tab. Only coordinators have it. Any coordinator can view it; only the assigned one can mark arrangements. Every other role sees 'You don't have access to this event.' (the Equipment tab's wording).</t>
+          <t>DECIDED 2026-10-08, not in the story: arrangements can be marked as not required, or as required again, only while the event is in Planning. On a Confirmed event, reversing a decision would leave a confirmed event with something outstanding (SPM-33-TC15). The server's refusal reads 'Arrangements can only be marked as not required while the event is in Planning.'</t>
         </is>
       </c>
       <c r="C6" s="11" t="n"/>
     </row>
-    <row r="7" ht="85" customHeight="1">
+    <row r="7" ht="71.5" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, not in the story: arrangements can be marked as not required, or as required again, only while the event is in Planning. On a Confirmed event, reversing a decision would leave a confirmed event with something outstanding (SPM-33-TC12). The server's refusal reads 'Arrangements can only be marked as not required while the event is in Planning.'</t>
+          <t>DECIDED 2026-10-08, not in the story: only an outstanding arrangement offers 'Mark as not required'. A complete one (an approved booking, reserved equipment) has nothing to waive; to drop it the Coordinator withdraws the booking or removes the requirement. The server's refusal reads 'Only an outstanding arrangement can be marked as not required.'</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
     </row>
-    <row r="8" ht="71.5" customHeight="1">
+    <row r="8" ht="166" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, not in the story: only an outstanding arrangement offers 'Mark as not required'. A complete one (an approved booking, reserved equipment) has nothing to waive; to drop it the Coordinator withdraws the booking or removes the requirement. The server's refusal reads 'Only an outstanding arrangement can be marked as not required.'</t>
+          <t>DECIDED 2026-10-09 (Kristen): who marked an arrangement as not required, and when, is recorded and shown on the item: 'Marked as not required by Daniel Tan on 8 Oct 2026, 11:00' (SPM-33-TC08, SPM-33-TC15). The customer briefing asks for it: 'Significant actions are recorded, including who performed the action and when it occurred' (Activity History), 'ConnectSphere should be able to determine what was changed, who changed it, and when' (8f Auditability, and answer #14). Reversing is stamped the same way, so the record is the latest decision on each arrangement, not a full history; answer #96 says a complete audit-history function is not required for Release 1. Marking still takes one click with no confirmation dialog, and no reason is asked for: none of the documents require one. Say so if the team wants a reason kept.</t>
         </is>
       </c>
       <c r="C8" s="11" t="n"/>
     </row>
-    <row r="9" ht="166" customHeight="1">
+    <row r="9" ht="125.5" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09 (Kristen): who marked an arrangement as not required, and when, is recorded and shown on the item: 'Marked as not required by Daniel Tan on 8 Oct 2026, 11:00' (SPM-33-TC05, SPM-33-TC12). The customer briefing asks for it: 'Significant actions are recorded, including who performed the action and when it occurred' (Activity History), 'ConnectSphere should be able to determine what was changed, who changed it, and when' (8f Auditability, and answer #14). Reversing is stamped the same way, so the record is the latest decision on each arrangement, not a full history; answer #96 says a complete audit-history function is not required for Release 1. Marking still takes one click with no confirmation dialog, and no reason is asked for: none of the documents require one. Say so if the team wants a reason kept.</t>
+          <t>DECIDED 2026-10-08, wording: the state labels 'Complete', 'Outstanding' and 'Not required'; the buttons 'Mark as not required' and 'Mark as required'; the summary '2 arrangements still block confirmation', '1 arrangement still blocks confirmation' and 'Nothing is blocking confirmation'; the items 'No venue booked' and 'Registration setup'; and the reasons 'is still awaiting a decision from Venue Staff', 'is not reserved yet', 'is flagged for review: &lt;why&gt;', 'registration is enabled but has no capacity' and 'registration is enabled but has no registration period'.</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
@@ -2530,65 +3291,76 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, wording: the state labels 'Complete', 'Outstanding' and 'Not required'; the buttons 'Mark as not required' and 'Mark as required'; the summary '2 arrangements still block confirmation', '1 arrangement still blocks confirmation' and 'Nothing is blocking confirmation'; the items 'No venue booked' and 'Registration setup'; and the reasons 'is still awaiting a decision from Venue Staff', 'is not reserved yet', 'is flagged for review: &lt;why&gt;', 'registration is enabled but has no capacity' and 'registration is enabled but has no registration period'.</t>
+          <t>DECIDED 2026-10-08, not in the story: what is listed. One item per pending or approved venue booking (a rejected or cancelled request is not listed), one item per equipment line, and 'Registration setup' only while registration is enabled. An event with registration switched off has no registration item (SPM-33-TC02), although the mockup design/mockups/Readiness.dc.html shows one reading 'Not required'. The mockup's 'Request reviewed and approved' and 'Technical support assigned' items are not listed either: nothing assigns technical support staff to an event yet.</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
     </row>
-    <row r="11" ht="125.5" customHeight="1">
+    <row r="11" ht="58" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, not in the story: what is listed. One item per pending or approved venue booking (a rejected or cancelled request is not listed), one item per equipment line, and 'Registration setup' only while registration is enabled. An event with registration switched off has no registration item (SPM-33-TC02), although the mockup design/mockups/Readiness.dc.html shows one reading 'Not required'. The mockup's 'Request reviewed and approved' and 'Technical support assigned' items are not listed either: nothing assigns technical support staff to an event yet.</t>
+          <t>DECIDED 2026-10-08, not in the story: the Readiness tab has no 'Confirm event' button, although the mockup shows one. Confirming stays on the Overview (SPM-34), which is why SPM-33-TC01 and SPM-33-TC13 go back to it.</t>
         </is>
       </c>
       <c r="C11" s="11" t="n"/>
     </row>
-    <row r="12" ht="58" customHeight="1">
+    <row r="12" ht="85" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08, not in the story: the Readiness tab has no 'Confirm event' button, although the mockup shows one. Confirming stays on the Overview (SPM-34), which is why SPM-33-TC01 and SPM-33-TC10 go back to it.</t>
+          <t>For Kayal (SPM-81) and Janelle (equipment, SPM-86): the migration 20261010100000_add_arrangement_not_required adds not_required, not_required_by and not_required_at to venue_bookings and to equipment_requests, which are their tables. It was applied to the shared database on 2026-10-10 and only adds columns. SPM-81's 'Request booking' flow is checked from the Readiness tab by SPM-33-TC04.</t>
         </is>
       </c>
       <c r="C12" s="11" t="n"/>
     </row>
-    <row r="13" ht="125.5" customHeight="1">
+    <row r="13" ht="85" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>For Kayal (SPM-81) and Janelle (equipment, SPM-86): the migration 20261010100000_add_arrangement_not_required adds not_required, not_required_by and not_required_at to venue_bookings and to equipment_requests, which are their tables. It was applied to the shared database on 2026-10-10 and only adds columns. When SPM-81 is merged in, SPM-33-TC01 and SPM-33-TC07 should be run again with bookings made through its screen. When SPM-86 is merged in, add the safety check item (AC6, AC9) as the header of src/lib/eventConfirmation.ts describes, and its cases here.</t>
+          <t>To check when Review Flagged Arrangements (SPM-68) is built: AC4 says a flagged arrangement is outstanding 'until the Coordinator resolves it'. Resolving is SPM-68's; in this story the only way a flagged arrangement stops blocking is to be marked as not required. Is that an acceptable way to resolve a flagged booking, or should a flagged arrangement not offer 'Mark as not required'?</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
     </row>
-    <row r="14" ht="85" customHeight="1">
+    <row r="14" ht="139" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>To check when Review Flagged Arrangements (SPM-68) is built: AC4 says a flagged arrangement is outstanding 'until the Coordinator resolves it'. Resolving is SPM-68's; in this story the only way a flagged arrangement stops blocking is to be marked as not required. Is that an acceptable way to resolve a flagged booking, or should a flagged arrangement not offer 'Mark as not required'?</t>
+          <t>DECIDED 2026-10-12 (Kristen): the safety check does not stop Confirm yet, as decided on 2026-10-08 - that gate is Resolve Safety Check Outcome's (SPM-88), and the Safety Officer's decision (SPM-87) is not built, so nothing could be confirmed if it did. So it is not counted in '... still block confirmation', and its item says 'Confirm event does not wait for it yet.' The one exception is a check awaiting review: the event is then in Safety review, which cannot move to Confirmed until the Safety Officer decides, so it IS counted (SPM-33-TC06). SPM-88 makes it always count by setting SAFETY_CHECK_BLOCKS_CONFIRMATION in src/lib/eventConfirmation.ts.</t>
         </is>
       </c>
       <c r="C14" s="11" t="n"/>
     </row>
-    <row r="15" ht="71.5" customHeight="1">
+    <row r="15" ht="125.5" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Merged with main on 2026-10-10, which brought Submit Event for Operational Safety Check (SPM-86). An arrangement marked as not required here no longer stops 'Submit for safety check' either (SPM-86 AC1: 'reserved or marked as not required'). AC6 and AC9 above can now be built: the Safety review status and the SafetyCheck record exist.</t>
+          <t>DECIDED 2026-10-12, wording: 'Operational Safety Check'; 'Not submitted', 'Awaiting review', 'Approved', 'Changes requested', 'Rejected'; 'the Operational Safety Check has not been submitted yet', 'is awaiting the Safety Officer's review', 'has to be submitted again', 'the Safety Officer asked for changes in the Operational Safety Check', 'the Safety Officer rejected the safety arrangement'; 'Submitted by &lt;name&gt; on &lt;date&gt;, &lt;time&gt;'; 'Confirm event does not wait for it yet.' The Safety Officer's reason or required changes are not shown here - viewing the decision is SPM-88's (its AC1).</t>
         </is>
       </c>
       <c r="C15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="71.5" customHeight="1">
+      <c r="A16" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>For SPM-87 (Conduct Operational Safety Check): there is no Safety Officer account or role in the app yet, so the fixtures for SPM-33-TC07 write the decision straight into the database with no Safety Officer named. Once SPM-87 is built, SPM-33-TC07 can be run on decisions made through its screen instead.</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2601,7 +3373,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -2628,25 +3400,37 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="125.5" customHeight="1">
+    <row r="3" ht="44.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Every venue booking, equipment line and the safety check are listed with their own status, and Confirm names what is outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Two Room Conference' is in Planning, assigned to Daniel Tan, with two venue bookings, Marina Auditorium (Approved) and Orchard Studio (Pending), and two equipment requirements, Handheld Wireless Mic (Reserved) and Audio Mixing Desk (Requested, not yet reviewed by Technical Support). Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123). Confirmation is refused in this case, so nothing is changed.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="85" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="5" ht="85" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM33 Two Room Conference' in the list
@@ -2657,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="85" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Event: SPM33 Two Room Conference (Planning)
 Venue bookings: Marina Auditorium (Approved), Orchard Studio (Pending)
@@ -2672,63 +3456,55 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="7" ht="301" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Step 2: The event opens with the status badge 'Planning' and a 'Readiness' tab after the 'Equipment' tab.
-Step 3: Four separate items are listed. 'Marina Auditorium' shows 'Approved' and 'Complete'. 'Orchard Studio' shows 'Pending' and 'Outstanding', and says it is still awaiting a decision from Venue Staff. 'Handheld Wireless Mic' shows 'Reserved' and 'Complete'. 'Audio Mixing Desk' shows 'Requested' and 'Outstanding', and says it is not reserved yet. Neither complete item shows 'Outstanding'. The message '2 arrangements still block confirmation' is shown above the list.
+Step 3: Five separate items are listed. 'Marina Auditorium' shows 'Approved' and 'Complete'. 'Orchard Studio' shows 'Pending' and 'Outstanding', and says it is still awaiting a decision from Venue Staff. 'Handheld Wireless Mic' shows 'Reserved' and 'Complete'. 'Audio Mixing Desk' shows 'Requested' and 'Outstanding', and says it is not reserved yet. Neither complete item shows 'Outstanding'. The last item, 'Operational Safety Check', shows 'Not submitted' and 'Outstanding', says the Operational Safety Check has not been submitted yet, and says 'Confirm event does not wait for it yet.' It has no 'Mark as not required' button, although 'Orchard Studio' and 'Audio Mixing Desk' do. The message '2 arrangements still block confirmation' is shown above the list: the safety check is not counted.
 Step 6: The event is NOT confirmed. The message 'This event cannot be confirmed yet: Orchard Studio for this event is still awaiting a decision from Venue Staff; Audio Mixing Desk for this event is not reserved yet.' is shown, naming the same two arrangements and neither of the complete ones. The status badge still reads 'Planning'.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -2736,7 +3512,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -2744,7 +3520,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -2752,10 +3528,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2768,7 +3552,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -2795,25 +3579,37 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>An event with no venue booking shows 'No venue booked', and nothing for equipment or registration it does not have</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Nothing Booked' is in Planning, assigned to Daniel Tan, and has no venue booking and no equipment requirements, and registration is not enabled. Logged in as Daniel Tan.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM33 Nothing Booked' in the list
@@ -2821,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Event: SPM33 Nothing Booked (Planning)
 Venue bookings: none
@@ -2836,61 +3632,53 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="71.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="7" ht="85" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: The list has one item, 'No venue booked', showing 'Outstanding' and saying no venue is booked for this event. It has no 'Mark as not required' button. No equipment item and no 'Registration setup' item is listed. The message '1 arrangement still blocks confirmation' is shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: Apart from the 'Operational Safety Check' (Not submitted), the list has one item, 'No venue booked', showing 'Outstanding' and saying no venue is booked for this event. It has no 'Mark as not required' button. No equipment item and no 'Registration setup' item is listed. The message '1 arrangement still blocks confirmation' is shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -2898,7 +3686,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -2906,7 +3694,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -2914,10 +3702,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2930,7 +3726,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -2957,25 +3753,37 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>A multi-session event shows which session each venue arrangement belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Two Day Forum' is in Planning, assigned to Daniel Tan, with two sessions, 'Day 1' and 'Day 2'. Day 1 has an approved booking at Orchard Seminar Room; Day 2 has no booking. Logged in as Daniel Tan.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM33 Two Day Forum' in the list
@@ -2983,13 +3791,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Event: SPM33 Two Day Forum (Planning), sessions Day 1 and Day 2
 Day 1: Orchard Seminar Room, Approved
@@ -2997,61 +3805,53 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Step 3: 'Orchard Seminar Room' is listed for 'Day 1' with 'Approved' and 'Complete'. A separate item 'No venue booked' is listed for 'Day 2' with 'Outstanding'. The message '1 arrangement still blocks confirmation' is shown.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -3059,7 +3859,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -3067,7 +3867,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -3075,10 +3875,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3091,7 +3899,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -3118,105 +3926,112 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="98.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Date Changed' is in Planning, assigned to Daniel Tan. Its venue booking at Orchard Seminar Room is Approved and its Handheld Wireless Mic is Reserved, but both were flagged for review when the event's date was changed. Logged in as Daniel Tan. Confirmation is refused in this case, so nothing is changed.</t>
+          <t>A second venue requested from the Venue tab is listed on its own, beside the first</t>
         </is>
       </c>
     </row>
     <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Run npm run fixtures:spm33 before and after this case: it sends a venue booking request. 'SPM33 Add A Breakout Room' is in Planning, assigned to Daniel Tan, on 2 Aug 2027, 09:00–13:00, with one venue booking, Marina Auditorium (Approved), and no equipment. Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="112" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Date Changed' in the list
-3. Click the 'Readiness' tab
-4. Click the 'Overview' tab
-5. Click 'Confirm event'
-6. Click 'Confirm event' in the dialog</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+2. Click 'SPM33 Add A Breakout Room' in the list
+3. Click the 'Venue' tab
+4. Click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
+5. Click 'Submit request'
+6. Click 'Back to Venue'
+7. Click the 'Readiness' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Date Changed (Planning)
-Venue: Orchard Seminar Room, Approved, flagged (the date or time changed)
-Equipment: Handheld Wireless Mic, Reserved, flagged (the date or time changed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="166" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Add A Breakout Room (Planning), 2 Aug 2027, 09:00–13:00
+Venue booking: Marina Auditorium, Approved
+Second venue requested: Orchard Seminar Room (ORC-SEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="193" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: 'Orchard Seminar Room' shows 'Approved' and 'Outstanding', not 'Complete', and says it is flagged for review: the date or time changed. 'Handheld Wireless Mic' shows 'Reserved' and 'Outstanding', and says it is flagged for review: the date or time changed. The message '2 arrangements still block confirmation' is shown.
-Step 6: The event is NOT confirmed. The message 'This event cannot be confirmed yet: Orchard Seminar Room for this event is flagged for review: the date or time changed; Handheld Wireless Mic for this event is flagged for review: the date or time changed.' is shown. The status badge still reads 'Planning'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 4: The 'Request a venue booking' page opens for 'SPM33 Add A Breakout Room' at 'Orchard Seminar Room (ORC-SEM)', with the event's own date and times.
+Step 5: A green alert 'Booking request sent to Venue Staff.' is shown.
+Step 6: The 'Booking requests' card lists 'Orchard Seminar Room (ORC-SEM)' with the 'Pending' badge, and the Marina Auditorium booking is still 'Approved'.
+Step 7: 'Marina Auditorium' and 'Orchard Seminar Room' are listed as two separate items. 'Marina Auditorium' shows 'Approved' and 'Complete'; 'Orchard Seminar Room' shows 'Pending' and 'Outstanding' and says it is still awaiting a decision from Venue Staff. The message '1 arrangement still blocks confirmation' is shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -3224,7 +4039,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -3232,7 +4047,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -3240,10 +4055,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3256,7 +4079,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -3283,103 +4106,109 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>A flagged venue booking and equipment reservation are shown as outstanding, with why, and prevent confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Run npm run fixtures:spm33 before this case. 'SPM33 Stage Unavailable' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and two equipment requirements: Handheld Wireless Mic (Reserved) and Portable Stage, which Technical Support marked 'Cannot be provided'. Logged in as Daniel Tan. This case changes the event. SPM-33-TC06 needs that change, so go straight to it and run npm run fixtures:spm33 after SPM-33-TC06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Date Changed' is in Planning, assigned to Daniel Tan. Its venue booking at Orchard Seminar Room is Approved and its Handheld Wireless Mic is Reserved, but both were flagged for review when the event's date was changed. Logged in as Daniel Tan. Confirmation is refused in this case, so nothing is changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="85" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Stage Unavailable' in the list
+2. Click 'SPM33 Date Changed' in the list
 3. Click the 'Readiness' tab
-4. Click 'Mark as not required' in the 'Portable Stage' item</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+4. Click the 'Overview' tab
+5. Click 'Confirm event'
+6. Click 'Confirm event' in the dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Stage Unavailable (Planning)
-Venue: Orchard Gallery, Approved
-Equipment: Handheld Wireless Mic (Reserved), Portable Stage (Cannot be provided)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="166" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Date Changed (Planning)
+Venue: Orchard Seminar Room, Approved, flagged (the date or time changed)
+Equipment: Handheld Wireless Mic, Reserved, flagged (the date or time changed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="166" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: 'Portable Stage' shows 'Cannot be provided' and 'Outstanding', with a 'Mark as not required' button. 'Orchard Gallery' and 'Handheld Wireless Mic' show 'Complete' and have no such button. The message '1 arrangement still blocks confirmation' is shown.
-Step 4: 'Portable Stage' now shows 'Not required' in place of 'Outstanding', and still shows 'Cannot be provided'. It says 'Marked as not required by Daniel Tan on' followed by today's date and the time. It reads differently from 'Handheld Wireless Mic', which shows 'Complete'. Its button now reads 'Mark as required'. The message changes to 'Nothing is blocking confirmation'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: 'Orchard Seminar Room' shows 'Approved' and 'Outstanding', not 'Complete', and says it is flagged for review: the date or time changed. 'Handheld Wireless Mic' shows 'Reserved' and 'Outstanding', and says it is flagged for review: the date or time changed. The message '2 arrangements still block confirmation' is shown.
+Step 6: The event is NOT confirmed. The message 'This event cannot be confirmed yet: Orchard Seminar Room for this event is flagged for review: the date or time changed; Handheld Wireless Mic for this event is flagged for review: the date or time changed.' is shown. The status badge still reads 'Planning'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -3387,7 +4216,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -3395,7 +4224,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -3403,10 +4232,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3419,7 +4256,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -3446,100 +4283,107 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>An event with the Safety Officer shows its safety check as awaiting review, and nothing can be marked</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>SPM-33-TC05 has just been run (so 'Portable Stage' on 'SPM33 Stage Unavailable' shows 'Not required') and the fixtures have NOT been reset since. Still logged in as Daniel Tan, on the Readiness tab of 'SPM33 Stage Unavailable'. Run npm run fixtures:spm33 after this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Mark as required' in the 'Portable Stage' item
-2. Click the 'Equipment' tab</t>
+          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Awaiting Safety Review' is in Safety review, assigned to Daniel Tan, with an approved venue booking at Orchard Gallery and a Handheld Wireless Mic (Reserved). Daniel Tan submitted it for an Operational Safety Check on 9 Oct 2026 at 14:30, and the Safety Officer has not decided yet. Logged in as Daniel Tan.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar
+2. Click 'SPM33 Awaiting Safety Review' in the list
+3. Click the 'Readiness' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Stage Unavailable (Planning)
-Equipment: Portable Stage (Cannot be provided), marked as not required in SPM-33-TC05</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="112" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM33 Awaiting Safety Review (Safety review)
+Venue: Orchard Gallery, Approved
+Equipment: Handheld Wireless Mic, Reserved
+Safety check: submitted by Daniel Tan, 9 Oct 2026, 14:30, awaiting review</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="152.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 1: 'Portable Stage' shows 'Outstanding' again, with a 'Mark as not required' button, and no longer says who marked it as not required. The message changes back to '1 arrangement still blocks confirmation'.
-Step 2: The 'Portable Stage' requirement is still listed with the status 'Cannot be provided' and its requested quantity. Marking it and reversing the decision did not change or remove the requirement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 2: The event opens with the status badge 'Safety review'.
+Step 3: 'Orchard Gallery' and 'Handheld Wireless Mic' show 'Complete'. The last item, 'Operational Safety Check', shows 'Awaiting review' and 'Outstanding', says the Operational Safety Check is awaiting the Safety Officer's review, and says 'Submitted by Daniel Tan on 9 Oct 2026, 14:30'. The message '1 arrangement still blocks confirmation' is shown: the event cannot be confirmed while the Safety Officer has it. No item has a 'Mark as not required' or 'Mark as required' button, because the event is not in Planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -3547,7 +4391,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -3555,7 +4399,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -3563,10 +4407,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3579,7 +4431,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -3606,104 +4458,112 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="17.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>A decided safety check shows the Safety Officer's decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Run npm run fixtures:spm33 before and after this case. 'SPM33 Breakout Not Needed' is in Planning, assigned to Daniel Tan, with two venue bookings: Marina Auditorium (Approved) and Orchard Studio (Pending). It has no equipment. Logged in as Daniel Tan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>The SPM-33 fixtures are loaded (npm run fixtures:spm33). 'SPM33 Safety Approved', 'SPM33 Safety Changes Requested' and 'SPM33 Safety Rejected' are in Planning, assigned to Daniel Tan, each with an approved venue booking at Orchard Gallery. Each was submitted for an Operational Safety Check by Daniel Tan on 9 Oct 2026 at 14:30, and the fixtures record the Safety Officer's decision on 10 Oct 2026: approved, changes requested and rejected respectively. Logged in as Daniel Tan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="125.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM33 Breakout Not Needed' in the list
+2. Click 'SPM33 Safety Approved' in the list
 3. Click the 'Readiness' tab
-4. Click 'Mark as not required' in the 'Orchard Studio' item
-5. Click the 'Venue' tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+4. Click 'All Events' in the sidebar
+5. Click 'SPM33 Safety Changes Requested' in the list
+6. Click the 'Readiness' tab
+7. Click 'All Events' in the sidebar
+8. Click 'SPM33 Safety Rejected' in the list
+9. Click the 'Readiness' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM33 Breakout Not Needed (Planning)
-Venue bookings: Marina Auditorium (Approved), Orchard Studio (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="139" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Events: SPM33 Safety Approved, SPM33 Safety Changes Requested, SPM33 Safety Rejected (all Planning)
+Safety checks: submitted 9 Oct 2026, 14:30, by Daniel Tan; decided 10 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="166" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: 'Orchard Studio' shows 'Pending' and 'Outstanding'. The message '1 arrangement still blocks confirmation' is shown.
-Step 4: 'Orchard Studio' shows 'Not required' and still shows 'Pending'. 'Marina Auditorium' still shows 'Approved' and 'Complete'. The message changes to 'Nothing is blocking confirmation'.
-Step 5: Under 'Booking requests', the Orchard Studio request is still listed as 'Pending' and the Marina Auditorium booking as 'Approved'. Neither was withdrawn or changed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: 'Operational Safety Check' shows 'Approved' and 'Complete', with 'Submitted by Daniel Tan on 9 Oct 2026, 14:30', and does not say 'Confirm event does not wait for it yet.' The message 'Nothing is blocking confirmation' is shown.
+Step 6: 'Operational Safety Check' shows 'Changes requested' and 'Outstanding', says the Safety Officer asked for changes in the Operational Safety Check, and says 'Confirm event does not wait for it yet.'
+Step 9: 'Operational Safety Check' shows 'Rejected' and 'Outstanding', says the Safety Officer rejected the safety arrangement, and says 'Confirm event does not wait for it yet.' It has no 'Mark as not required' button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>kchoongg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -3711,7 +4571,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -3719,7 +4579,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -3727,10 +4587,18 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/test-cases/SPM-33_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-33_Test_Cases.xlsx
@@ -2729,7 +2729,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="98.5" customHeight="1">
+    <row r="7" ht="112" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2738,7 +2738,7 @@
       <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Step 2: The event opens with the status badge 'Confirmed'.
-Step 3: 'Orchard Gallery' shows 'Complete'. 'Portable Stage' shows 'Not required' and 'Cannot be provided', and says 'Marked as not required by Daniel Tan on 1 Oct 2026, 10:00'. There is no 'Mark as required' or 'Mark as not required' button on any item: arrangements are marked only while the event is in Planning.</t>
+Step 3: The message 'This event is confirmed' is shown in place of the count of blocking arrangements. 'Orchard Gallery' shows 'Complete'. 'Portable Stage' shows 'Not required' and 'Cannot be provided', and says 'Marked as not required by Daniel Tan on 1 Oct 2026, 10:00'. There is no 'Mark as required' or 'Mark as not required' button on any item: arrangements are marked only while the event is in Planning.</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3361,6 +3361,17 @@
         </is>
       </c>
       <c r="C16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="179.5" customHeight="1">
+      <c r="A17" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-12, layout (cleaned up for a first-time user): the Readiness tab groups its items into 'Venue bookings', 'Equipment', 'Registration' and 'Safety check' sections. Every item shows where it stands ('Complete', 'Outstanding' or 'Not required') first, in the same place, then its name, then the action. Its own status is written out with what it is the status of - 'Booking status: Pending', 'Request status: Reserved', 'Safety check status: Awaiting review' - so it is not mistaken for whether it is done. A key under the summary says what the three states mean: 'In place.', 'Still to be done.', 'Marked as not needed for this event.' An empty section says 'No equipment has been recorded for this event.' or 'Registration is not enabled for this event.' A confirmed event shows 'This event is confirmed' instead of the blocking count, and its subtitle reads 'What this event was confirmed with.'</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3632,7 +3643,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="85" customHeight="1">
+    <row r="7" ht="112" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3640,7 +3651,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: Apart from the 'Operational Safety Check' (Not submitted), the list has one item, 'No venue booked', showing 'Outstanding' and saying no venue is booked for this event. It has no 'Mark as not required' button. No equipment item and no 'Registration setup' item is listed. The message '1 arrangement still blocks confirmation' is shown.</t>
+          <t>Step 3: Apart from the 'Operational Safety Check' (Not submitted), the list has one item, 'No venue booked', showing 'Outstanding' and saying no venue is booked for this event. It has no 'Mark as not required' button. The Equipment section says 'No equipment has been recorded for this event.' and the Registration section says 'Registration is not enabled for this event.' The message '1 arrangement still blocks confirmation' is shown.</t>
         </is>
       </c>
     </row>
